--- a/Projects/Airfoil Project/vpm_results.xlsx
+++ b/Projects/Airfoil Project/vpm_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Brinton/Personal/School/Aerodynamics/Projects/Airfoil Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF230D03-3611-3249-B2CF-914F089D1366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD71B38-57AE-414C-8005-B1900C903401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17980" activeTab="2" xr2:uid="{78CCE67D-3157-0E4F-B537-1D5EA6E851EB}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17960" activeTab="1" xr2:uid="{78CCE67D-3157-0E4F-B537-1D5EA6E851EB}"/>
   </bookViews>
   <sheets>
     <sheet name="2412" sheetId="1" r:id="rId1"/>
@@ -121,10 +121,10 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4655,24 +4655,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="K1" s="5" t="s">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="K1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -4719,11 +4719,11 @@
       <c r="B3">
         <v>-1.1843399999999999</v>
       </c>
-      <c r="C3">
-        <v>0.23805000000000001</v>
-      </c>
-      <c r="D3">
-        <v>-5.1569999999999998E-2</v>
+      <c r="C3" s="5">
+        <v>0.24912999999999999</v>
+      </c>
+      <c r="D3" s="5">
+        <v>-4.0480000000000002E-2</v>
       </c>
       <c r="F3">
         <v>-12</v>
@@ -4747,11 +4747,11 @@
       <c r="B4">
         <v>-0.94564000000000004</v>
       </c>
-      <c r="C4">
-        <v>0.18074000000000001</v>
-      </c>
-      <c r="D4">
-        <v>-5.2080000000000001E-2</v>
+      <c r="C4" s="5">
+        <v>0.19014</v>
+      </c>
+      <c r="D4" s="5">
+        <v>-4.2680000000000003E-2</v>
       </c>
       <c r="F4">
         <f>F3+2</f>
@@ -4776,11 +4776,11 @@
       <c r="B5">
         <v>-0.70577999999999996</v>
       </c>
-      <c r="C5">
-        <v>0.12212000000000001</v>
-      </c>
-      <c r="D5">
-        <v>-5.2609999999999997E-2</v>
+      <c r="C5" s="5">
+        <v>0.12973000000000001</v>
+      </c>
+      <c r="D5" s="5">
+        <v>-4.4999999999999998E-2</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F17" si="2">F4+2</f>
@@ -4805,11 +4805,11 @@
       <c r="B6">
         <v>-0.46505000000000002</v>
       </c>
-      <c r="C6">
-        <v>6.2449999999999999E-2</v>
-      </c>
-      <c r="D6">
-        <v>-5.3170000000000002E-2</v>
+      <c r="C6" s="5">
+        <v>6.8190000000000001E-2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>-4.7440000000000003E-2</v>
       </c>
       <c r="F6">
         <f t="shared" si="2"/>
@@ -4834,11 +4834,11 @@
       <c r="B7">
         <v>-0.22377</v>
       </c>
-      <c r="C7">
-        <v>2E-3</v>
-      </c>
-      <c r="D7">
-        <v>-5.3809999999999997E-2</v>
+      <c r="C7" s="5">
+        <v>5.8100000000000001E-3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-4.999E-2</v>
       </c>
       <c r="F7">
         <f t="shared" si="2"/>
@@ -4863,11 +4863,11 @@
       <c r="B8">
         <v>1.779E-2</v>
       </c>
-      <c r="C8">
-        <v>-5.8979999999999998E-2</v>
-      </c>
-      <c r="D8">
-        <v>-5.4530000000000002E-2</v>
+      <c r="C8" s="5">
+        <v>-5.7090000000000002E-2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-5.2639999999999999E-2</v>
       </c>
       <c r="F8">
         <f t="shared" si="2"/>
@@ -4892,10 +4892,10 @@
       <c r="B9">
         <v>0.25933</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="5">
         <v>-0.1202</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="5">
         <v>-5.5370000000000003E-2</v>
       </c>
       <c r="F9">
@@ -4921,11 +4921,11 @@
       <c r="B10">
         <v>0.50055000000000005</v>
       </c>
-      <c r="C10">
-        <v>-0.18140000000000001</v>
-      </c>
-      <c r="D10">
-        <v>-5.6340000000000001E-2</v>
+      <c r="C10" s="5">
+        <v>-0.18323</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-5.8169999999999999E-2</v>
       </c>
       <c r="F10">
         <f t="shared" si="2"/>
@@ -4950,11 +4950,11 @@
       <c r="B11">
         <v>0.74116000000000004</v>
       </c>
-      <c r="C11">
-        <v>-0.24229999999999999</v>
-      </c>
-      <c r="D11">
-        <v>-5.7459999999999997E-2</v>
+      <c r="C11" s="5">
+        <v>-0.24587000000000001</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-6.1030000000000001E-2</v>
       </c>
       <c r="F11">
         <f t="shared" si="2"/>
@@ -4979,11 +4979,11 @@
       <c r="B12">
         <v>0.98087000000000002</v>
       </c>
-      <c r="C12">
-        <v>-0.30263000000000001</v>
-      </c>
-      <c r="D12">
-        <v>-5.876E-2</v>
+      <c r="C12" s="5">
+        <v>-0.30780000000000002</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-6.3930000000000001E-2</v>
       </c>
       <c r="F12">
         <f t="shared" si="2"/>
@@ -5008,11 +5008,11 @@
       <c r="B13">
         <v>1.21939</v>
       </c>
-      <c r="C13">
-        <v>-0.36210999999999999</v>
-      </c>
-      <c r="D13">
-        <v>-6.0229999999999999E-2</v>
+      <c r="C13" s="5">
+        <v>-0.36874000000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-6.6860000000000003E-2</v>
       </c>
       <c r="F13">
         <f t="shared" si="2"/>
@@ -5037,11 +5037,11 @@
       <c r="B14">
         <v>1.45642</v>
       </c>
-      <c r="C14">
-        <v>-0.42047000000000001</v>
-      </c>
-      <c r="D14">
-        <v>-6.1899999999999997E-2</v>
+      <c r="C14" s="5">
+        <v>-0.42836999999999997</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-6.9800000000000001E-2</v>
       </c>
       <c r="F14">
         <f t="shared" si="2"/>
@@ -5066,11 +5066,11 @@
       <c r="B15">
         <v>1.69167</v>
       </c>
-      <c r="C15">
-        <v>-0.47744999999999999</v>
-      </c>
-      <c r="D15">
-        <v>-6.3769999999999993E-2</v>
+      <c r="C15" s="5">
+        <v>-0.48641000000000001</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-7.2739999999999999E-2</v>
       </c>
       <c r="F15">
         <f t="shared" si="2"/>
@@ -5095,11 +5095,11 @@
       <c r="B16">
         <v>1.92486</v>
       </c>
-      <c r="C16">
-        <v>-0.53278000000000003</v>
-      </c>
-      <c r="D16">
-        <v>-6.5860000000000002E-2</v>
+      <c r="C16" s="5">
+        <v>-0.54259000000000002</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-7.5660000000000005E-2</v>
       </c>
       <c r="F16">
         <f>F15+2</f>
@@ -5124,11 +5124,11 @@
       <c r="B17">
         <v>2.15571</v>
       </c>
-      <c r="C17">
-        <v>-0.58621000000000001</v>
-      </c>
-      <c r="D17">
-        <v>-6.8159999999999998E-2</v>
+      <c r="C17" s="5">
+        <v>-0.59660999999999997</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-7.8560000000000005E-2</v>
       </c>
       <c r="F17">
         <f t="shared" si="2"/>
@@ -5165,24 +5165,24 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="K1" s="5" t="s">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="K1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -5226,15 +5226,11 @@
       <c r="A3">
         <v>-12</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>-1.25946</v>
       </c>
-      <c r="C3" s="6">
-        <v>0.27356000000000003</v>
-      </c>
-      <c r="D3" s="6">
-        <v>-3.4419999999999999E-2</v>
-      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
       <c r="F3">
         <v>-12</v>
       </c>
@@ -5254,15 +5250,11 @@
         <f>A3+2</f>
         <v>-10</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>-1.00407</v>
       </c>
-      <c r="C4" s="6">
-        <v>0.20942</v>
-      </c>
-      <c r="D4" s="6">
-        <v>-3.7789999999999997E-2</v>
-      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
       <c r="F4">
         <f>F3+2</f>
         <v>-10</v>
@@ -5283,15 +5275,11 @@
         <f t="shared" ref="A5:A17" si="1">A4+2</f>
         <v>-8</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>-0.74744999999999995</v>
       </c>
-      <c r="C5" s="6">
-        <v>0.14385000000000001</v>
-      </c>
-      <c r="D5" s="6">
-        <v>-4.1189999999999997E-2</v>
-      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
       <c r="F5">
         <f t="shared" ref="F5:F17" si="2">F4+2</f>
         <v>-8</v>
@@ -5312,15 +5300,11 @@
         <f t="shared" si="1"/>
         <v>-6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>-0.48992000000000002</v>
       </c>
-      <c r="C6" s="6">
-        <v>7.7109999999999998E-2</v>
-      </c>
-      <c r="D6" s="6">
-        <v>-4.4699999999999997E-2</v>
-      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
       <c r="F6">
         <f t="shared" si="2"/>
         <v>-6</v>
@@ -5341,15 +5325,11 @@
         <f t="shared" si="1"/>
         <v>-4</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>-0.23179</v>
       </c>
-      <c r="C7" s="6">
-        <v>9.4299999999999991E-3</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-4.8379999999999999E-2</v>
-      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
       <c r="F7">
         <f t="shared" si="2"/>
         <v>-4</v>
@@ -5370,15 +5350,11 @@
         <f t="shared" si="1"/>
         <v>-2</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>2.6620000000000001E-2</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.8950000000000002E-2</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-5.2299999999999999E-2</v>
-      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
       <c r="F8">
         <f t="shared" si="2"/>
         <v>-2</v>
@@ -5399,15 +5375,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>0.28499999999999998</v>
       </c>
-      <c r="C9" s="6">
-        <v>-0.12776999999999999</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-5.6520000000000001E-2</v>
-      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
       <c r="F9">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -5428,15 +5400,11 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>0.54303000000000001</v>
       </c>
-      <c r="C10" s="6">
-        <v>-0.19678000000000001</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-6.1100000000000002E-2</v>
-      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
       <c r="F10">
         <f t="shared" si="2"/>
         <v>2</v>
@@ -5457,15 +5425,11 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>0.8004</v>
       </c>
-      <c r="C11" s="6">
-        <v>-0.26571</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-6.6100000000000006E-2</v>
-      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
       <c r="F11">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -5486,15 +5450,11 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>1.0567899999999999</v>
       </c>
-      <c r="C12" s="6">
-        <v>-0.33429999999999999</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-7.1550000000000002E-2</v>
-      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
       <c r="F12">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -5515,15 +5475,11 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>1.31189</v>
       </c>
-      <c r="C13" s="6">
-        <v>-0.40228000000000003</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-7.7499999999999999E-2</v>
-      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
       <c r="F13">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -5544,15 +5500,11 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>1.5653999999999999</v>
       </c>
-      <c r="C14" s="6">
-        <v>-0.46938999999999997</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-8.3989999999999995E-2</v>
-      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
       <c r="F14">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -5573,15 +5525,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>1.8169999999999999</v>
       </c>
-      <c r="C15" s="6">
-        <v>-0.53537000000000001</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-9.1050000000000006E-2</v>
-      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
       <c r="F15">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -5602,15 +5550,11 @@
         <f>A15+2</f>
         <v>14</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>2.0663900000000002</v>
       </c>
-      <c r="C16" s="6">
-        <v>-0.59994000000000003</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-9.869E-2</v>
-      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
       <c r="F16">
         <f>F15+2</f>
         <v>14</v>
@@ -5631,15 +5575,11 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>2.3132600000000001</v>
       </c>
-      <c r="C17" s="6">
-        <v>-0.66285000000000005</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.10693999999999999</v>
-      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
       <c r="F17">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -5684,24 +5624,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="K1" s="5" t="s">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="K1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -5751,12 +5691,8 @@
       <c r="B3" s="3">
         <v>-1.47119</v>
       </c>
-      <c r="C3" s="3">
-        <v>0.3695</v>
-      </c>
-      <c r="D3" s="3">
-        <v>9.7400000000000004E-3</v>
-      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3">
         <v>-12</v>
@@ -5793,12 +5729,8 @@
       <c r="B4" s="3">
         <v>-1.2287399999999999</v>
       </c>
-      <c r="C4" s="3">
-        <v>0.31039</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7.8700000000000003E-3</v>
-      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3">
         <f>F3+2</f>
@@ -5837,12 +5769,8 @@
       <c r="B5" s="3">
         <v>-0.98479000000000005</v>
       </c>
-      <c r="C5" s="3">
-        <v>0.24994</v>
-      </c>
-      <c r="D5" s="3">
-        <v>6.1399999999999996E-3</v>
-      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3">
         <f t="shared" ref="F5:F17" si="3">F4+2</f>
@@ -5881,12 +5809,8 @@
       <c r="B6" s="3">
         <v>-0.73965000000000003</v>
       </c>
-      <c r="C6" s="3">
-        <v>0.18840999999999999</v>
-      </c>
-      <c r="D6" s="3">
-        <v>4.5100000000000001E-3</v>
-      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3">
         <f t="shared" si="3"/>
@@ -5925,12 +5849,8 @@
       <c r="B7" s="3">
         <v>-0.49359999999999998</v>
       </c>
-      <c r="C7" s="3">
-        <v>0.12606000000000001</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2.96E-3</v>
-      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3">
         <f t="shared" si="3"/>
@@ -5969,12 +5889,8 @@
       <c r="B8" s="3">
         <v>-0.24695</v>
       </c>
-      <c r="C8" s="3">
-        <v>6.3170000000000004E-2</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1.47E-3</v>
-      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3">
         <f t="shared" si="3"/>
@@ -6013,12 +5929,8 @@
       <c r="B9" s="3">
         <v>0</v>
       </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3">
         <f t="shared" si="3"/>
@@ -6057,12 +5969,8 @@
       <c r="B10" s="3">
         <v>0.24695</v>
       </c>
-      <c r="C10" s="3">
-        <v>-6.3170000000000004E-2</v>
-      </c>
-      <c r="D10" s="3">
-        <v>-1.47E-3</v>
-      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3">
         <f t="shared" si="3"/>
@@ -6101,12 +6009,8 @@
       <c r="B11" s="3">
         <v>0.49359999999999998</v>
       </c>
-      <c r="C11" s="3">
-        <v>-0.12606999999999999</v>
-      </c>
-      <c r="D11" s="3">
-        <v>-2.97E-3</v>
-      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3">
         <f t="shared" si="3"/>
@@ -6145,12 +6049,8 @@
       <c r="B12" s="3">
         <v>0.73965000000000003</v>
       </c>
-      <c r="C12" s="3">
-        <v>-0.18842999999999999</v>
-      </c>
-      <c r="D12" s="3">
-        <v>-4.5300000000000002E-3</v>
-      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3">
         <f t="shared" si="3"/>
@@ -6189,12 +6089,8 @@
       <c r="B13" s="3">
         <v>0.98479000000000005</v>
       </c>
-      <c r="C13" s="3">
-        <v>-0.24998000000000001</v>
-      </c>
-      <c r="D13" s="3">
-        <v>-6.1799999999999997E-3</v>
-      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3">
         <f t="shared" si="3"/>
@@ -6233,12 +6129,8 @@
       <c r="B14" s="3">
         <v>1.2287399999999999</v>
       </c>
-      <c r="C14" s="3">
-        <v>-0.31046000000000001</v>
-      </c>
-      <c r="D14" s="3">
-        <v>-7.9399999999999991E-3</v>
-      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3">
         <f t="shared" si="3"/>
@@ -6277,12 +6169,8 @@
       <c r="B15" s="3">
         <v>1.47119</v>
       </c>
-      <c r="C15" s="3">
-        <v>-0.36959999999999998</v>
-      </c>
-      <c r="D15" s="3">
-        <v>-9.8399999999999998E-3</v>
-      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3">
         <f t="shared" si="3"/>
@@ -6321,12 +6209,8 @@
       <c r="B16" s="3">
         <v>1.71184</v>
       </c>
-      <c r="C16" s="3">
-        <v>-0.42714999999999997</v>
-      </c>
-      <c r="D16" s="3">
-        <v>-1.1900000000000001E-2</v>
-      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3">
         <f>F15+2</f>
@@ -6365,12 +6249,8 @@
       <c r="B17" s="3">
         <v>1.95041</v>
       </c>
-      <c r="C17" s="3">
-        <v>-0.48286000000000001</v>
-      </c>
-      <c r="D17" s="3">
-        <v>-1.414E-2</v>
-      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3">
         <f t="shared" si="3"/>
